--- a/outputs/01a0ee28-cea0-7d82-b0a7-f548e4c665b0/Combat_Stats.xlsx
+++ b/outputs/01a0ee28-cea0-7d82-b0a7-f548e4c665b0/Combat_Stats.xlsx
@@ -25,7 +25,14 @@
     <x:comment ref="C11" authorId="0">
       <x:text>
         <x:r>
-          <x:t>Current lab placeholder. User has judged 300 HP too low. Final boss HP is TBD.</x:t>
+          <x:t>Provisional runtime value, set 2026-10-09 for playtesting (raised from the 300 lab placeholder the user judged too low). Final boss HP is TBD.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="B12" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>Provisional: three handgun hits. Body contact and the discharge stay lethal; knife and stomp cannot hit it. Added 2026-10-09 for the Green Zone boss's second phase.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -248,8 +255,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EnemyValues" displayName="EnemyValues" ref="A4:J11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EnemyValues" displayName="EnemyValues" ref="A4:J12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J12"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Enemy"/>
     <x:tableColumn id="2" name="HP"/>
@@ -807,7 +814,7 @@
         <x:v>TBD</x:v>
       </x:c>
       <x:c r="C11" s="14" t="n">
-        <x:v>300</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D11" s="17" t="n">
         <x:v>0.5</x:v>
@@ -834,19 +841,40 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
-      <x:c r="I12" s="2"/>
-      <x:c r="J12" s="2"/>
+      <x:c r="A12" s="2" t="str">
+        <x:v>Shootable flying machine</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="n">
+        <x:f>'Attacks'!$D$12</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="H12" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="I12" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="B5:B11">
+  <x:conditionalFormatting sqref="B5:B12">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TBD"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/01a0ee28-cea0-7d82-b0a7-f548e4c665b0/Combat_Stats.xlsx
+++ b/outputs/01a0ee28-cea0-7d82-b0a7-f548e4c665b0/Combat_Stats.xlsx
@@ -274,8 +274,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AttackValues" displayName="AttackValues" ref="A4:E152" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E152"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AttackValues" displayName="AttackValues" ref="A4:E160" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E160"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Actor"/>
     <x:tableColumn id="2" name="Attack / category"/>
@@ -3455,6 +3455,142 @@
         <x:v>frames</x:v>
       </x:c>
     </x:row>
+    <x:row r="153" ht="23" customHeight="1">
+      <x:c r="A153" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B153" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C153" s="2" t="str">
+        <x:v>Canisters per lob</x:v>
+      </x:c>
+      <x:c r="D153" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E153" s="2" t="str">
+        <x:v>count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="23" customHeight="1">
+      <x:c r="A154" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B154" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C154" s="2" t="str">
+        <x:v>Canister spread</x:v>
+      </x:c>
+      <x:c r="D154" s="13" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="E154" s="2" t="str">
+        <x:v>m</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="23" customHeight="1">
+      <x:c r="A155" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B155" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C155" s="2" t="str">
+        <x:v>Cooldown</x:v>
+      </x:c>
+      <x:c r="D155" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E155" s="2" t="str">
+        <x:v>s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="23" customHeight="1">
+      <x:c r="A156" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B156" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C156" s="2" t="str">
+        <x:v>Ground-camping trigger</x:v>
+      </x:c>
+      <x:c r="D156" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E156" s="2" t="str">
+        <x:v>s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="23" customHeight="1">
+      <x:c r="A157" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B157" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C157" s="2" t="str">
+        <x:v>Fire patch width</x:v>
+      </x:c>
+      <x:c r="D157" s="13" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="E157" s="2" t="str">
+        <x:v>m</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="23" customHeight="1">
+      <x:c r="A158" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B158" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C158" s="2" t="str">
+        <x:v>Fire burn time</x:v>
+      </x:c>
+      <x:c r="D158" s="13" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E158" s="2" t="str">
+        <x:v>s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="23" customHeight="1">
+      <x:c r="A159" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B159" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C159" s="2" t="str">
+        <x:v>Fire damage while standing in it, per second</x:v>
+      </x:c>
+      <x:c r="D159" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E159" s="2" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="23" customHeight="1">
+      <x:c r="A160" s="2" t="str">
+        <x:v>Launcher boss</x:v>
+      </x:c>
+      <x:c r="B160" s="2" t="str">
+        <x:v>Firebomb lob (arena)</x:v>
+      </x:c>
+      <x:c r="C160" s="2" t="str">
+        <x:v>Fire damage for landing on it (puts it out)</x:v>
+      </x:c>
+      <x:c r="D160" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E160" s="2" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R126c719027594fc0"/>

--- a/outputs/01a0ee28-cea0-7d82-b0a7-f548e4c665b0/Combat_Stats.xlsx
+++ b/outputs/01a0ee28-cea0-7d82-b0a7-f548e4c665b0/Combat_Stats.xlsx
@@ -808,7 +808,7 @@
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>TBD</x:v>
@@ -2029,7 +2029,7 @@
     </x:row>
     <x:row r="69" ht="23" customHeight="1">
       <x:c r="A69" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B69" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2046,7 +2046,7 @@
     </x:row>
     <x:row r="70" ht="23" customHeight="1">
       <x:c r="A70" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B70" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2063,7 +2063,7 @@
     </x:row>
     <x:row r="71" ht="23" customHeight="1">
       <x:c r="A71" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B71" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2080,7 +2080,7 @@
     </x:row>
     <x:row r="72" ht="23" customHeight="1">
       <x:c r="A72" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B72" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2097,7 +2097,7 @@
     </x:row>
     <x:row r="73" ht="23" customHeight="1">
       <x:c r="A73" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B73" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2114,7 +2114,7 @@
     </x:row>
     <x:row r="74" ht="23" customHeight="1">
       <x:c r="A74" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B74" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2131,7 +2131,7 @@
     </x:row>
     <x:row r="75" ht="23" customHeight="1">
       <x:c r="A75" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B75" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2148,7 +2148,7 @@
     </x:row>
     <x:row r="76" ht="23" customHeight="1">
       <x:c r="A76" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B76" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2165,7 +2165,7 @@
     </x:row>
     <x:row r="77" ht="23" customHeight="1">
       <x:c r="A77" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B77" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2182,7 +2182,7 @@
     </x:row>
     <x:row r="78" ht="23" customHeight="1">
       <x:c r="A78" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B78" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2199,7 +2199,7 @@
     </x:row>
     <x:row r="79" ht="23" customHeight="1">
       <x:c r="A79" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B79" s="2" t="str">
         <x:v>Missile salvo</x:v>
@@ -2216,7 +2216,7 @@
     </x:row>
     <x:row r="80" ht="23" customHeight="1">
       <x:c r="A80" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B80" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2233,7 +2233,7 @@
     </x:row>
     <x:row r="81" ht="23" customHeight="1">
       <x:c r="A81" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B81" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2250,7 +2250,7 @@
     </x:row>
     <x:row r="82" ht="23" customHeight="1">
       <x:c r="A82" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B82" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2267,7 +2267,7 @@
     </x:row>
     <x:row r="83" ht="23" customHeight="1">
       <x:c r="A83" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B83" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2284,7 +2284,7 @@
     </x:row>
     <x:row r="84" ht="23" customHeight="1">
       <x:c r="A84" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B84" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2301,7 +2301,7 @@
     </x:row>
     <x:row r="85" ht="23" customHeight="1">
       <x:c r="A85" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B85" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2318,7 +2318,7 @@
     </x:row>
     <x:row r="86" ht="23" customHeight="1">
       <x:c r="A86" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B86" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2335,7 +2335,7 @@
     </x:row>
     <x:row r="87" ht="23" customHeight="1">
       <x:c r="A87" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B87" s="2" t="str">
         <x:v>Rocket flight</x:v>
@@ -2352,7 +2352,7 @@
     </x:row>
     <x:row r="88" ht="23" customHeight="1">
       <x:c r="A88" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B88" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2369,7 +2369,7 @@
     </x:row>
     <x:row r="89" ht="23" customHeight="1">
       <x:c r="A89" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B89" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2386,7 +2386,7 @@
     </x:row>
     <x:row r="90" ht="23" customHeight="1">
       <x:c r="A90" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B90" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2403,7 +2403,7 @@
     </x:row>
     <x:row r="91" ht="23" customHeight="1">
       <x:c r="A91" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B91" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2420,7 +2420,7 @@
     </x:row>
     <x:row r="92" ht="23" customHeight="1">
       <x:c r="A92" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B92" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2437,7 +2437,7 @@
     </x:row>
     <x:row r="93" ht="23" customHeight="1">
       <x:c r="A93" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B93" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2454,7 +2454,7 @@
     </x:row>
     <x:row r="94" ht="23" customHeight="1">
       <x:c r="A94" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B94" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2471,7 +2471,7 @@
     </x:row>
     <x:row r="95" ht="23" customHeight="1">
       <x:c r="A95" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B95" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2488,7 +2488,7 @@
     </x:row>
     <x:row r="96" ht="23" customHeight="1">
       <x:c r="A96" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B96" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2505,7 +2505,7 @@
     </x:row>
     <x:row r="97" ht="23" customHeight="1">
       <x:c r="A97" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B97" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2522,7 +2522,7 @@
     </x:row>
     <x:row r="98" ht="23" customHeight="1">
       <x:c r="A98" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B98" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2539,7 +2539,7 @@
     </x:row>
     <x:row r="99" ht="23" customHeight="1">
       <x:c r="A99" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B99" s="2" t="str">
         <x:v>Jump / landing</x:v>
@@ -2556,7 +2556,7 @@
     </x:row>
     <x:row r="100" ht="23" customHeight="1">
       <x:c r="A100" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B100" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2573,7 +2573,7 @@
     </x:row>
     <x:row r="101" ht="23" customHeight="1">
       <x:c r="A101" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B101" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2590,7 +2590,7 @@
     </x:row>
     <x:row r="102" ht="23" customHeight="1">
       <x:c r="A102" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B102" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2607,7 +2607,7 @@
     </x:row>
     <x:row r="103" ht="23" customHeight="1">
       <x:c r="A103" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B103" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2624,7 +2624,7 @@
     </x:row>
     <x:row r="104" ht="23" customHeight="1">
       <x:c r="A104" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B104" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2641,7 +2641,7 @@
     </x:row>
     <x:row r="105" ht="23" customHeight="1">
       <x:c r="A105" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B105" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2658,7 +2658,7 @@
     </x:row>
     <x:row r="106" ht="23" customHeight="1">
       <x:c r="A106" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B106" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2675,7 +2675,7 @@
     </x:row>
     <x:row r="107" ht="23" customHeight="1">
       <x:c r="A107" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B107" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2692,7 +2692,7 @@
     </x:row>
     <x:row r="108" ht="23" customHeight="1">
       <x:c r="A108" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B108" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2709,7 +2709,7 @@
     </x:row>
     <x:row r="109" ht="23" customHeight="1">
       <x:c r="A109" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B109" s="2" t="str">
         <x:v>Opening charge</x:v>
@@ -2726,7 +2726,7 @@
     </x:row>
     <x:row r="110" ht="23" customHeight="1">
       <x:c r="A110" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B110" s="2" t="str">
         <x:v>Firing shove</x:v>
@@ -2743,7 +2743,7 @@
     </x:row>
     <x:row r="111" ht="23" customHeight="1">
       <x:c r="A111" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B111" s="2" t="str">
         <x:v>Firing shove</x:v>
@@ -2760,7 +2760,7 @@
     </x:row>
     <x:row r="112" ht="23" customHeight="1">
       <x:c r="A112" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B112" s="2" t="str">
         <x:v>Firing shove</x:v>
@@ -2777,7 +2777,7 @@
     </x:row>
     <x:row r="113" ht="23" customHeight="1">
       <x:c r="A113" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B113" s="2" t="str">
         <x:v>Firing shove</x:v>
@@ -2794,7 +2794,7 @@
     </x:row>
     <x:row r="114" ht="23" customHeight="1">
       <x:c r="A114" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B114" s="2" t="str">
         <x:v>Firing shove</x:v>
@@ -2811,7 +2811,7 @@
     </x:row>
     <x:row r="115" ht="23" customHeight="1">
       <x:c r="A115" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B115" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2828,7 +2828,7 @@
     </x:row>
     <x:row r="116" ht="23" customHeight="1">
       <x:c r="A116" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B116" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2845,7 +2845,7 @@
     </x:row>
     <x:row r="117" ht="23" customHeight="1">
       <x:c r="A117" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B117" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2862,7 +2862,7 @@
     </x:row>
     <x:row r="118" ht="23" customHeight="1">
       <x:c r="A118" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B118" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2879,7 +2879,7 @@
     </x:row>
     <x:row r="119" ht="23" customHeight="1">
       <x:c r="A119" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B119" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2896,7 +2896,7 @@
     </x:row>
     <x:row r="120" ht="23" customHeight="1">
       <x:c r="A120" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B120" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2913,7 +2913,7 @@
     </x:row>
     <x:row r="121" ht="23" customHeight="1">
       <x:c r="A121" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B121" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2930,7 +2930,7 @@
     </x:row>
     <x:row r="122" ht="23" customHeight="1">
       <x:c r="A122" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B122" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -2947,7 +2947,7 @@
     </x:row>
     <x:row r="123" ht="23" customHeight="1">
       <x:c r="A123" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B123" s="2" t="str">
         <x:v>Head-contact smoke</x:v>
@@ -3355,7 +3355,7 @@
     </x:row>
     <x:row r="147" ht="23" customHeight="1">
       <x:c r="A147" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B147" s="2" t="str">
         <x:v>Movement / reaction</x:v>
@@ -3372,7 +3372,7 @@
     </x:row>
     <x:row r="148" ht="23" customHeight="1">
       <x:c r="A148" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B148" s="2" t="str">
         <x:v>Movement / reaction</x:v>
@@ -3389,7 +3389,7 @@
     </x:row>
     <x:row r="149" ht="23" customHeight="1">
       <x:c r="A149" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B149" s="2" t="str">
         <x:v>Movement / reaction</x:v>
@@ -3406,7 +3406,7 @@
     </x:row>
     <x:row r="150" ht="23" customHeight="1">
       <x:c r="A150" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B150" s="2" t="str">
         <x:v>Movement / reaction</x:v>
@@ -3423,7 +3423,7 @@
     </x:row>
     <x:row r="151" ht="23" customHeight="1">
       <x:c r="A151" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B151" s="2" t="str">
         <x:v>Movement / reaction</x:v>
@@ -3440,7 +3440,7 @@
     </x:row>
     <x:row r="152" ht="23" customHeight="1">
       <x:c r="A152" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B152" s="2" t="str">
         <x:v>Movement / reaction</x:v>
@@ -3457,7 +3457,7 @@
     </x:row>
     <x:row r="153" ht="23" customHeight="1">
       <x:c r="A153" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B153" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3474,7 +3474,7 @@
     </x:row>
     <x:row r="154" ht="23" customHeight="1">
       <x:c r="A154" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B154" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3491,7 +3491,7 @@
     </x:row>
     <x:row r="155" ht="23" customHeight="1">
       <x:c r="A155" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B155" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3508,7 +3508,7 @@
     </x:row>
     <x:row r="156" ht="23" customHeight="1">
       <x:c r="A156" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B156" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3525,7 +3525,7 @@
     </x:row>
     <x:row r="157" ht="23" customHeight="1">
       <x:c r="A157" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B157" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3542,7 +3542,7 @@
     </x:row>
     <x:row r="158" ht="23" customHeight="1">
       <x:c r="A158" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B158" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3559,7 +3559,7 @@
     </x:row>
     <x:row r="159" ht="23" customHeight="1">
       <x:c r="A159" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B159" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
@@ -3576,7 +3576,7 @@
     </x:row>
     <x:row r="160" ht="23" customHeight="1">
       <x:c r="A160" s="2" t="str">
-        <x:v>Launcher boss</x:v>
+        <x:v>S.T.O.M.P.</x:v>
       </x:c>
       <x:c r="B160" s="2" t="str">
         <x:v>Firebomb lob (arena)</x:v>
